--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,27 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,23 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1003,24 +1007,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>3</v>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,27 +1980,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,23 +2120,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2151,31 +2155,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,27 +2495,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2685,23 +2685,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2712,27 +2716,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2743,17 +2747,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2770,17 +2774,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2824,27 +2828,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2855,20 +2855,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>3</v>
@@ -2882,27 +2886,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3406,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3437,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3472,27 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4169,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4204,27 +4200,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4239,27 +4235,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4274,27 +4266,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4305,27 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5090,23 +5090,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5117,27 +5121,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5148,27 +5152,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,27 +5336,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5371,29 +5371,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
         <v>3</v>
       </c>
@@ -5406,23 +5398,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5437,31 +5429,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -5472,31 +5464,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5507,27 +5499,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5542,17 +5534,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5569,21 +5561,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5596,31 +5592,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5631,25 +5627,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5662,17 +5654,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5689,31 +5681,23 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,7 +5708,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5734,21 +5718,21 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5759,31 +5743,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5794,23 +5774,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -5825,23 +5809,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5852,23 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,23 +6313,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,27 +6348,31 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -6379,31 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -6414,27 +6414,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -6993,27 +6993,31 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -7024,31 +7028,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -7059,27 +7063,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,27 +7241,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -7272,17 +7268,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7299,27 +7295,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -7330,17 +7322,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7357,17 +7349,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7384,20 +7376,24 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7411,17 +7407,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7438,23 +7434,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,23 +7492,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7519,24 +7523,20 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -7775,27 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7841,31 +7845,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7880,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7915,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,23 +8306,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8337,31 +8341,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -8372,27 +8376,23 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,27 +9201,23 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -9232,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9259,17 +9259,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -9286,20 +9286,24 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9313,23 +9317,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -9340,24 +9348,20 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9371,17 +9375,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9398,17 +9402,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9425,27 +9429,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9537,31 +9537,31 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -9572,23 +9572,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9603,27 +9607,31 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -9634,7 +9642,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9644,17 +9652,21 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -9696,31 +9708,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -9731,31 +9739,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -9766,27 +9770,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9801,31 +9805,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -10429,20 +10429,24 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10456,24 +10460,20 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -11209,17 +11209,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11236,23 +11236,23 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,31 +11561,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -11596,23 +11592,23 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -11627,27 +11623,31 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,31 +13706,27 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13741,27 +13737,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13776,27 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13807,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,23 +13869,27 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -13896,27 +13900,23 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13954,20 +13954,24 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13981,23 +13985,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14008,27 +14016,23 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -14039,24 +14043,20 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
         <v>3</v>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,31 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472">
@@ -14259,23 +14255,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,27 +14290,23 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14325,27 +14321,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,31 +14356,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
+      <c r="F475" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -14395,27 +14391,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14430,23 +14426,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,23 +14461,23 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.127</t>
         </is>
       </c>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14492,19 +14492,19 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14512,11 +14512,11 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -14527,31 +14527,31 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -15027,23 +15027,27 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -15058,23 +15062,27 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G497" t="n">
@@ -15089,31 +15097,31 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -15124,31 +15132,27 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -15159,27 +15163,23 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.5%</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -16154,25 +16154,21 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>216.25K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F537" t="inlineStr"/>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16185,31 +16181,23 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -16220,29 +16208,21 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
       <c r="G539" t="n">
         <v>3</v>
       </c>
@@ -16255,31 +16235,23 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
       <c r="G540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -16290,17 +16262,17 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E541" t="inlineStr"/>
@@ -16317,21 +16289,29 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G542" t="n">
         <v>3</v>
       </c>
@@ -16344,23 +16324,31 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -16371,21 +16359,25 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16398,23 +16390,31 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -16564,23 +16564,27 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -16591,17 +16595,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="E552" t="inlineStr"/>
@@ -16618,20 +16622,24 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.18M</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
         <v>3</v>
@@ -16645,17 +16653,17 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
@@ -16672,23 +16680,27 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr"/>
+          <t>4.07M</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -16699,17 +16711,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16726,27 +16738,23 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -16757,17 +16765,17 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E558" t="inlineStr"/>
@@ -16784,24 +16792,20 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>-1.2M</t>
-        </is>
-      </c>
+          <t>0.872M</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="n">
         <v>3</v>
@@ -16815,17 +16819,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="E560" t="inlineStr"/>
@@ -16842,27 +16846,23 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>6.87%</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -16984,20 +16984,24 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr"/>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F567" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17015,27 +17019,23 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G568" t="n">
@@ -17050,27 +17050,27 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G569" t="n">
@@ -17788,23 +17788,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17819,27 +17815,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17877,23 +17869,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -17904,19 +17900,23 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -18020,23 +18020,19 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -18082,19 +18078,23 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G605" t="n">
@@ -18136,19 +18136,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18190,19 +18190,19 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -18217,19 +18217,19 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -18328,15 +18328,19 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>$21.53T</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -18370,19 +18374,15 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+      <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="inlineStr"/>
       <c r="G617" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="618">
@@ -18485,13 +18485,13 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
@@ -18531,13 +18531,13 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E624" t="inlineStr"/>
@@ -18554,19 +18554,19 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
@@ -18577,19 +18577,19 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -18753,23 +18753,19 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18842,19 +18838,23 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -18892,19 +18892,19 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -19076,13 +19076,13 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
@@ -19122,19 +19122,19 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="650">
@@ -19145,13 +19145,13 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
@@ -19168,13 +19168,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19191,19 +19191,19 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -19214,13 +19214,13 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
@@ -19237,13 +19237,13 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
@@ -19260,19 +19260,19 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
@@ -19413,17 +19413,21 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19467,21 +19471,17 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F664" t="inlineStr"/>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -19873,13 +19873,13 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -19893,7 +19893,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
@@ -19935,18 +19935,18 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
@@ -19955,7 +19955,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -19997,27 +19997,23 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
       <c r="F682" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -20028,23 +20024,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -20055,23 +20055,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685">
@@ -20082,27 +20086,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686">
@@ -20113,27 +20117,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -20144,19 +20148,19 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -20171,19 +20175,19 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G688" t="n">
@@ -20198,23 +20202,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20229,27 +20233,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -20260,27 +20264,23 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G691" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="692">
@@ -20399,13 +20399,21 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
-      <c r="D696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
       <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G696" t="n">
         <v>2</v>
       </c>
@@ -20418,19 +20426,23 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="E697" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G697" t="n">
@@ -20445,25 +20457,13 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -20503,16 +20503,16 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
-      <c r="E700" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-196Bcf</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr"/>
       <c r="G700" t="n">
         <v>3</v>
@@ -20526,16 +20526,16 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>-196Bcf</t>
-        </is>
-      </c>
-      <c r="E701" t="inlineStr"/>
+      <c r="D701" t="inlineStr"/>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="F701" t="inlineStr"/>
       <c r="G701" t="n">
         <v>3</v>
@@ -20595,13 +20595,13 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E704" t="inlineStr"/>
@@ -20622,13 +20622,13 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E705" t="inlineStr"/>
@@ -20856,13 +20856,13 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E715" t="inlineStr"/>
@@ -20879,13 +20879,13 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E716" t="inlineStr"/>
@@ -21360,27 +21360,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F735" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
@@ -21422,27 +21422,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="738">
@@ -21453,27 +21453,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -21515,19 +21515,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21542,23 +21546,23 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -21573,23 +21577,23 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -21604,23 +21608,19 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G743" t="n">
@@ -21905,23 +21905,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -21932,23 +21932,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G755" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="756">
@@ -21986,19 +21986,19 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G757" t="n">
@@ -22013,19 +22013,19 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G758" t="n">
@@ -22067,23 +22067,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="778">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="785">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22949,23 +22949,23 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G798" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="799">
@@ -22976,23 +22976,23 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G799" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="800">
@@ -23003,19 +23003,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23030,23 +23030,23 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="802">
@@ -23084,19 +23084,19 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G803" t="n">
@@ -23111,19 +23111,19 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G804" t="n">
@@ -23138,23 +23138,23 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806">
@@ -23165,7 +23165,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -23173,7 +23173,7 @@
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr"/>
       <c r="G806" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -23306,7 +23306,7 @@
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="814">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -23344,7 +23344,7 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -23363,7 +23363,7 @@
       <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="817">
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -23507,15 +23507,11 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>15.6M</t>
-        </is>
-      </c>
+      <c r="D824" t="inlineStr"/>
       <c r="E824" t="inlineStr"/>
       <c r="F824" t="inlineStr"/>
       <c r="G824" t="n">
@@ -23530,11 +23526,15 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
-      <c r="D825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>15.6M</t>
+        </is>
+      </c>
       <c r="E825" t="inlineStr"/>
       <c r="F825" t="inlineStr"/>
       <c r="G825" t="n">
@@ -23710,15 +23710,23 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="E833" t="inlineStr"/>
-      <c r="F833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>$273.0B</t>
+        </is>
+      </c>
       <c r="G833" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="834">
@@ -23871,23 +23879,15 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
+      <c r="D840" t="inlineStr"/>
       <c r="E840" t="inlineStr"/>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>$-103B</t>
-        </is>
-      </c>
+      <c r="F840" t="inlineStr"/>
       <c r="G840" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="841">
@@ -23898,13 +23898,21 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
       <c r="E841" t="inlineStr"/>
-      <c r="F841" t="inlineStr"/>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>$-103B</t>
+        </is>
+      </c>
       <c r="G841" t="n">
         <v>2</v>
       </c>
@@ -23917,21 +23925,13 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr"/>
       <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>$376.0B</t>
-        </is>
-      </c>
+      <c r="F842" t="inlineStr"/>
       <c r="G842" t="n">
         <v>2</v>
       </c>
@@ -23944,19 +23944,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,24 +833,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>3</v>
@@ -864,23 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,27 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,23 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1980,31 +1984,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2081,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2116,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,31 +2507,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2685,27 +2685,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2716,27 +2712,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2747,20 +2739,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>3</v>
@@ -2774,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2828,17 +2824,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2855,27 +2851,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2886,23 +2882,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3406,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4204,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,27 +4235,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -4266,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4301,31 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,27 +5032,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -5063,23 +5059,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -5090,27 +5090,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -5152,17 +5152,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,27 +5336,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5371,23 +5371,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5398,23 +5406,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5429,31 +5441,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5464,7 +5472,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5474,21 +5482,21 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5499,31 +5507,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5561,25 +5561,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5592,31 +5588,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5627,21 +5623,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5654,17 +5654,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5681,23 +5681,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5708,31 +5716,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -5743,23 +5751,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5774,29 +5782,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
         <v>3</v>
       </c>
@@ -5809,27 +5809,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5844,31 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -6313,27 +6317,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,31 +6352,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6383,23 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6414,27 +6418,23 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -6993,31 +6993,31 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -7028,27 +7028,23 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -7063,27 +7059,31 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7349,20 +7357,24 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7376,24 +7388,20 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7407,17 +7415,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7434,27 +7442,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7469,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,27 +7496,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,31 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7740,31 +7736,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -7775,31 +7771,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7880,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7915,27 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,27 +8306,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8341,31 +8337,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -8376,23 +8372,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,27 +9228,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,17 +9255,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -9286,24 +9282,20 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9317,27 +9309,23 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -9348,20 +9336,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9375,17 +9367,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9402,23 +9394,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -9429,23 +9425,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,27 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9607,31 +9603,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -9642,31 +9634,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9708,27 +9696,31 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9739,23 +9731,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9770,31 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9805,7 +9801,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9815,17 +9811,21 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -10429,24 +10429,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10460,20 +10456,24 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,23 +11561,23 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -11592,27 +11592,31 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -11623,31 +11627,27 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,27 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,27 +13741,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13772,31 +13776,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13811,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,27 +13869,23 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -13900,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13927,20 +13927,24 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
         <v>3</v>
@@ -13954,24 +13958,20 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13985,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,23 +14012,27 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -14043,17 +14043,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,31 +14259,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -14290,23 +14294,23 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.127</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14321,27 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14356,19 +14360,19 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14376,11 +14380,11 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -14391,27 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14426,27 +14430,23 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,23 +14461,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14492,31 +14496,31 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
+      <c r="F479" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -14527,31 +14531,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -15027,27 +15027,23 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>77.5%</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -15062,31 +15058,31 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -15097,31 +15093,27 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -15132,23 +15124,27 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr"/>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G499" t="n">
@@ -15163,23 +15159,27 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -16154,21 +16154,25 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16181,23 +16185,31 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -16208,21 +16220,29 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G539" t="n">
         <v>3</v>
       </c>
@@ -16235,17 +16255,17 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E540" t="inlineStr"/>
@@ -16262,23 +16282,31 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -16289,29 +16317,21 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
       <c r="G542" t="n">
         <v>3</v>
       </c>
@@ -16324,31 +16344,23 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
       <c r="G543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -16359,25 +16371,21 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>216.25K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F544" t="inlineStr"/>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16390,31 +16398,23 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
       <c r="G545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -16564,27 +16564,23 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>6.87%</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="552">
@@ -16595,17 +16591,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="E552" t="inlineStr"/>
@@ -16622,24 +16618,20 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>-1.2M</t>
-        </is>
-      </c>
+          <t>0.872M</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
         <v>3</v>
@@ -16653,17 +16645,17 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
@@ -16680,27 +16672,23 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr"/>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="556">
@@ -16711,17 +16699,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16738,23 +16726,27 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr"/>
+          <t>4.07M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -16765,20 +16757,24 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>0.18M</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="n">
         <v>3</v>
@@ -16792,17 +16788,17 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="E559" t="inlineStr"/>
@@ -16819,23 +16815,27 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F560" t="inlineStr"/>
       <c r="G560" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -16846,17 +16846,17 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E561" t="inlineStr"/>
@@ -16984,27 +16984,27 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -17019,20 +17019,24 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr"/>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F568" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17050,27 +17054,23 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G569" t="n">
@@ -17788,19 +17788,23 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17815,23 +17819,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -17869,27 +17877,23 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -17900,23 +17904,19 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -18020,19 +18020,19 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -18047,27 +18047,27 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -18078,27 +18078,27 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -18136,19 +18136,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18753,19 +18753,23 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18838,23 +18842,19 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
       <c r="F637" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -18892,19 +18892,19 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -19076,13 +19076,13 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
@@ -19122,13 +19122,13 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
@@ -19145,13 +19145,13 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
@@ -19168,13 +19168,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19191,19 +19191,19 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19214,13 +19214,13 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
@@ -19260,19 +19260,19 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="656">
@@ -19873,23 +19873,23 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G678" t="n">
@@ -19935,27 +19935,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -20024,27 +20024,23 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -20055,13 +20051,13 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -20075,7 +20071,7 @@
         </is>
       </c>
       <c r="G684" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20086,18 +20082,18 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
@@ -20106,7 +20102,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -20117,23 +20113,23 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G686" t="n">
@@ -20148,23 +20144,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
@@ -20175,23 +20175,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689">
@@ -20202,27 +20206,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G689" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="690">
@@ -20233,23 +20237,19 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr"/>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G690" t="n">
@@ -20264,19 +20264,19 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20426,25 +20426,13 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E697" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
       <c r="G697" t="n">
         <v>2</v>
       </c>
@@ -20457,13 +20445,25 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -21360,27 +21360,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="736">
@@ -21422,27 +21422,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="738">
@@ -21453,27 +21453,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F738" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
@@ -21515,23 +21515,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21546,23 +21546,23 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -21577,23 +21577,19 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -21608,19 +21604,23 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G743" t="n">
@@ -21932,23 +21932,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G755" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="756">
@@ -22067,23 +22067,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="778">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22949,23 +22949,23 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G798" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="799">
@@ -22976,23 +22976,23 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G799" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800">
@@ -23003,19 +23003,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23030,19 +23030,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23084,23 +23084,23 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="804">
@@ -23111,19 +23111,19 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G804" t="n">
@@ -23138,23 +23138,23 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G805" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="806">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -23344,7 +23344,7 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="816">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -23401,7 +23401,7 @@
       <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="819">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,17 +833,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,27 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,23 +918,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -949,23 +949,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,24 +980,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>3</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,27 +1984,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2015,31 +2019,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,23 +2054,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2081,31 +2089,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2116,27 +2124,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2151,31 +2155,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,31 +2495,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,23 +2712,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2739,27 +2743,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,17 +2774,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2824,20 +2828,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>3</v>
@@ -2851,27 +2859,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2882,27 +2886,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3406,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3437,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3472,27 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4204,27 +4200,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4235,31 +4235,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4270,27 +4270,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4301,27 +4305,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,27 +4340,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5059,27 +5059,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5090,27 +5090,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5121,27 +5121,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5152,17 +5148,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5179,23 +5175,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,31 +5336,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -5371,27 +5363,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5406,29 +5398,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
         <v>3</v>
       </c>
@@ -5441,23 +5425,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5472,31 +5456,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -5507,23 +5491,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5534,17 +5526,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5561,21 +5553,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5588,7 +5584,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5598,21 +5594,21 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5623,25 +5619,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5654,17 +5646,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5681,31 +5673,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5716,31 +5708,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5751,23 +5739,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5782,23 +5774,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5809,27 +5809,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5844,31 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -6282,31 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -6317,27 +6313,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6352,23 +6344,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6383,27 +6379,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6418,27 +6414,31 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7028,27 +7024,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -7059,31 +7059,31 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,27 +7268,23 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7299,17 +7295,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7326,27 +7322,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7357,24 +7349,20 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7388,17 +7376,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7415,23 +7403,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7442,17 +7434,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7469,23 +7461,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -7496,17 +7492,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7523,20 +7519,24 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,27 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7736,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7806,27 +7810,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7841,31 +7845,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7880,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,23 +8306,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8337,31 +8341,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -8372,27 +8376,23 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,23 +9259,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -9282,20 +9290,24 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9309,17 +9321,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9336,24 +9348,20 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9367,17 +9375,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9394,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9425,27 +9429,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9547,17 +9547,21 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -9568,31 +9572,31 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9603,23 +9607,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9634,27 +9642,31 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -9696,31 +9708,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -9731,27 +9739,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9766,31 +9774,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -9801,31 +9805,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -10429,20 +10429,24 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10456,24 +10460,20 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,17 +11182,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,23 +11263,23 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,27 +11561,31 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -11592,31 +11596,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,27 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13667,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,31 +13702,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13741,27 +13737,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13776,31 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13811,27 +13807,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,23 +13869,27 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -13896,27 +13900,23 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -13927,24 +13927,20 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
         <v>3</v>
@@ -13958,17 +13954,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -13985,23 +13981,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14012,27 +14012,23 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -14043,17 +14039,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,20 +14066,24 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
         <v>3</v>
@@ -14224,27 +14224,23 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14259,31 +14255,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -14294,23 +14286,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14325,27 +14321,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,31 +14356,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
+      <c r="F475" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -14395,27 +14391,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14430,23 +14426,23 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.127</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,31 +14457,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -14496,19 +14492,19 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14516,11 +14512,11 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -15027,23 +15027,27 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -15058,31 +15062,27 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -15093,23 +15093,27 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr"/>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G498" t="n">
@@ -15124,27 +15128,23 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.5%</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G499" t="n">
@@ -15159,31 +15159,31 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -16154,25 +16154,21 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>216.25K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F537" t="inlineStr"/>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16185,31 +16181,23 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -16220,29 +16208,21 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
       <c r="G539" t="n">
         <v>3</v>
       </c>
@@ -16255,23 +16235,31 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -16282,31 +16270,23 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
       <c r="G541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -16317,21 +16297,29 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G542" t="n">
         <v>3</v>
       </c>
@@ -16344,23 +16332,31 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -16371,21 +16367,25 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16398,17 +16398,17 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E545" t="inlineStr"/>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E551" t="inlineStr"/>
@@ -16591,23 +16591,27 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -16618,17 +16622,17 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="E553" t="inlineStr"/>
@@ -16645,20 +16649,24 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>0.18M</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="n">
         <v>3</v>
@@ -16672,23 +16680,27 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr"/>
+          <t>4.07M</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -16699,17 +16711,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16726,27 +16738,23 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -16757,24 +16765,20 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>-1.2M</t>
-        </is>
-      </c>
+          <t>0.872M</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="n">
         <v>3</v>
@@ -16788,17 +16792,17 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="E559" t="inlineStr"/>
@@ -16815,27 +16819,23 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>6.87%</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
       <c r="F560" t="inlineStr"/>
       <c r="G560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -16846,17 +16846,17 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E561" t="inlineStr"/>
@@ -16984,27 +16984,23 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -17019,27 +17015,27 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G568" t="n">
@@ -17054,20 +17050,24 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr"/>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F569" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17788,23 +17788,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17819,27 +17815,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17877,23 +17869,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -17904,19 +17900,23 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -18020,19 +18020,19 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -18078,27 +18078,23 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -18136,23 +18132,27 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G607" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -18753,23 +18753,19 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18842,19 +18838,23 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -18892,19 +18892,19 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -19076,13 +19076,13 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
@@ -19122,13 +19122,13 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
@@ -19145,13 +19145,13 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
@@ -19168,13 +19168,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19191,19 +19191,19 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -19214,19 +19214,19 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -19237,19 +19237,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655">
@@ -19260,13 +19260,13 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
@@ -19873,27 +19873,27 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="679">
@@ -19935,23 +19935,19 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E680" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr"/>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G680" t="n">
@@ -20024,19 +20020,19 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G683" t="n">
@@ -20051,23 +20047,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -20082,27 +20078,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20113,27 +20109,23 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -20144,13 +20136,13 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -20164,7 +20156,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -20175,18 +20167,18 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -20195,7 +20187,7 @@
         </is>
       </c>
       <c r="G688" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
@@ -20206,23 +20198,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20237,23 +20229,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G690" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691">
@@ -20264,23 +20260,27 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr"/>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G691" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="692">
@@ -20426,13 +20426,25 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="G697" t="n">
         <v>2</v>
       </c>
@@ -20445,25 +20457,13 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -21360,27 +21360,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -21422,27 +21422,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F737" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
@@ -21453,27 +21453,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="739">
@@ -21515,23 +21515,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21546,23 +21546,19 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E741" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr"/>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -21577,19 +21573,23 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -21604,23 +21604,23 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G743" t="n">
@@ -21932,23 +21932,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G755" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="756">
@@ -22067,23 +22067,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="778">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="785">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22949,23 +22949,23 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G798" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799">
@@ -22976,23 +22976,23 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G799" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="800">
@@ -23003,19 +23003,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23030,23 +23030,23 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="802">
@@ -23084,23 +23084,23 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G803" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="804">
@@ -23111,19 +23111,19 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G804" t="n">
@@ -23138,19 +23138,19 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G805" t="n">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -23344,7 +23344,7 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -23401,7 +23401,7 @@
       <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="819">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,23 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -833,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -887,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -918,24 +918,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>3</v>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1030,27 +1030,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,23 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1980,27 +1984,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2011,31 +2019,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2046,27 +2054,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2081,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2116,27 +2120,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2151,31 +2155,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,31 +2495,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2685,27 +2685,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2743,23 +2743,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,17 +2774,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2824,27 +2828,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2855,27 +2855,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2886,20 +2882,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>3</v>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3406,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3437,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3472,27 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -4165,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4200,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,27 +4235,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,27 +4270,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4301,27 +4305,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,31 +4336,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4618,23 +4618,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,27 +5005,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -5036,17 +5036,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5063,27 +5063,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,17 +5117,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5148,17 +5144,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5175,27 +5171,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5206,23 +5202,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -5336,31 +5336,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -5371,31 +5371,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -5406,27 +5398,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5441,29 +5433,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
         <v>3</v>
       </c>
@@ -5476,23 +5460,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5507,31 +5491,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5542,17 +5526,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5569,21 +5553,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5596,31 +5584,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5631,25 +5615,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5662,17 +5642,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5689,7 +5669,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5699,21 +5679,21 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,23 +5704,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -5755,23 +5739,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -5782,27 +5774,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -5817,23 +5809,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5844,31 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,31 +6317,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -6352,27 +6348,23 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6387,27 +6379,31 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -6418,23 +6414,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -6993,31 +6993,31 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -7028,27 +7028,23 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -7063,27 +7059,31 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -7241,27 +7241,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -7272,17 +7268,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7299,27 +7295,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -7330,17 +7322,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7357,20 +7349,24 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7384,24 +7380,20 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7415,17 +7407,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7442,23 +7434,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7469,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7496,23 +7492,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7740,27 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7841,31 +7845,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,23 +8306,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8337,31 +8341,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -8372,27 +8376,23 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,23 +9201,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -9228,17 +9232,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9255,23 +9259,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -9282,20 +9290,24 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9309,17 +9321,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9336,24 +9348,20 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9367,27 +9375,23 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -9398,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,27 +9537,31 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -9568,7 +9572,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9578,17 +9582,21 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -9599,31 +9607,31 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -9634,23 +9642,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9696,27 +9708,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9731,31 +9743,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -9766,31 +9774,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -9801,31 +9805,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -10429,20 +10429,24 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10456,24 +10460,20 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,23 +11155,23 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -11182,17 +11182,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -11209,17 +11209,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11236,23 +11236,23 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,23 +11561,23 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -11592,27 +11592,31 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -11623,31 +11627,27 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,31 +13706,27 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13741,27 +13737,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13776,27 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13807,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -13842,24 +13842,20 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
         <v>3</v>
@@ -13873,23 +13869,27 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -13900,27 +13900,23 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -13931,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13958,17 +13954,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -13985,23 +13981,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14012,27 +14012,23 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -14043,20 +14039,24 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
         <v>3</v>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,27 +14259,23 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,31 +14290,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -14325,27 +14321,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,31 +14356,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
+      <c r="F475" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -14395,27 +14391,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14430,31 +14426,31 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -14465,23 +14461,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14496,19 +14496,19 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14516,11 +14516,11 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14531,23 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.127</t>
         </is>
       </c>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -15027,31 +15027,27 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -15062,27 +15058,23 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>77.5%</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G497" t="n">
@@ -15097,23 +15089,27 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G498" t="n">
@@ -15128,31 +15124,31 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -15163,23 +15159,27 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr"/>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -16154,25 +16154,21 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>216.25K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F537" t="inlineStr"/>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16185,31 +16181,23 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -16220,29 +16208,21 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
       <c r="G539" t="n">
         <v>3</v>
       </c>
@@ -16255,17 +16235,17 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E540" t="inlineStr"/>
@@ -16282,23 +16262,31 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -16309,21 +16297,29 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G542" t="n">
         <v>3</v>
       </c>
@@ -16336,23 +16332,31 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -16363,21 +16367,25 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16390,31 +16398,23 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
       <c r="G545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E551" t="inlineStr"/>
@@ -16591,17 +16591,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E552" t="inlineStr"/>
@@ -16618,23 +16618,27 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -16645,17 +16649,17 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
@@ -16672,23 +16676,27 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr"/>
+          <t>4.07M</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -16699,24 +16707,20 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>-1.2M</t>
-        </is>
-      </c>
+          <t>0.872M</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="n">
         <v>3</v>
@@ -16730,27 +16734,23 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -16761,17 +16761,17 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="E558" t="inlineStr"/>
@@ -16788,27 +16788,23 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>6.87%</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
@@ -16819,17 +16815,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E560" t="inlineStr"/>
@@ -16846,20 +16842,24 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>0.18M</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="n">
         <v>3</v>
@@ -16984,27 +16984,27 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -17019,20 +17019,24 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr"/>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F568" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17050,27 +17054,23 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G569" t="n">
@@ -17788,23 +17788,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17819,27 +17815,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17877,23 +17869,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -17904,19 +17900,23 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -18020,27 +18020,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18078,27 +18074,27 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -18136,19 +18132,23 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18753,23 +18753,19 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18842,19 +18838,23 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -18892,19 +18892,19 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -19076,13 +19076,13 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
@@ -19122,19 +19122,19 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -19145,19 +19145,19 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
       <c r="F650" t="inlineStr"/>
       <c r="G650" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="651">
@@ -19168,13 +19168,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19191,19 +19191,19 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -19214,13 +19214,13 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
@@ -19237,13 +19237,13 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
@@ -19260,13 +19260,13 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
@@ -19873,27 +19873,23 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E678" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr"/>
       <c r="F678" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
@@ -19935,13 +19931,13 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -19955,7 +19951,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -20024,18 +20020,18 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
@@ -20044,7 +20040,7 @@
         </is>
       </c>
       <c r="G683" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -20055,23 +20051,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -20086,23 +20082,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686">
@@ -20113,23 +20113,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr"/>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
@@ -20140,27 +20144,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -20171,23 +20175,19 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G688" t="n">
@@ -20202,19 +20202,19 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20229,23 +20229,23 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G690" t="n">
@@ -20260,27 +20260,27 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G691" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="692">
@@ -20426,13 +20426,25 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="G697" t="n">
         <v>2</v>
       </c>
@@ -20445,25 +20457,13 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -21360,27 +21360,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="736">
@@ -21422,27 +21422,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="738">
@@ -21453,27 +21453,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F738" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
@@ -21515,19 +21515,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21542,23 +21546,23 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -21573,23 +21577,23 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -21604,23 +21608,19 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G743" t="n">
@@ -21932,23 +21932,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G755" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="756">
@@ -22067,23 +22067,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="778">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="785">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22949,19 +22949,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -22976,19 +22976,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23003,23 +23003,23 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G800" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="801">
@@ -23030,23 +23030,23 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="802">
@@ -23084,23 +23084,23 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G803" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="804">
@@ -23111,23 +23111,23 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -23138,19 +23138,19 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G805" t="n">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -23344,7 +23344,7 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -23401,7 +23401,7 @@
       <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="819">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -837,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,23 +1003,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1030,24 +1034,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>3</v>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,31 +1984,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2019,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2054,23 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,31 +2507,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2685,27 +2685,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2716,20 +2712,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>3</v>
@@ -2743,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2774,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2828,23 +2824,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2882,27 +2882,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3406,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4169,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4204,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,27 +4239,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4305,27 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4978,23 +4978,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -5005,27 +5009,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -5036,17 +5040,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5063,17 +5067,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5090,17 +5094,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5117,17 +5121,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5144,17 +5148,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5171,27 +5175,23 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -5202,27 +5202,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -5336,31 +5336,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -5371,23 +5371,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5398,27 +5406,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5433,23 +5441,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5460,23 +5476,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5491,7 +5511,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5501,21 +5521,21 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5526,17 +5546,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5553,25 +5573,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5584,23 +5600,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5615,21 +5631,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5642,17 +5662,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5669,31 +5689,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -5704,29 +5724,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
         <v>3</v>
       </c>
@@ -5739,27 +5751,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5774,31 +5786,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5809,31 +5813,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5844,31 +5848,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,23 +6313,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,27 +6348,31 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -6379,31 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -6414,27 +6414,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7028,27 +7024,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -7059,31 +7059,31 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7349,24 +7357,20 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7380,17 +7384,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7407,17 +7411,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7434,27 +7438,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,27 +7492,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7523,20 +7519,24 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,27 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -7740,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7775,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7810,31 +7810,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,27 +8306,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8341,31 +8337,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -8376,23 +8372,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,27 +9201,23 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -9232,17 +9228,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9259,27 +9255,23 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -9290,24 +9282,20 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9321,23 +9309,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -9348,20 +9340,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9375,23 +9371,27 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,31 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9607,31 +9599,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -9642,27 +9630,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9708,31 +9696,31 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9743,7 +9731,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9753,17 +9741,21 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9774,27 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9805,23 +9801,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -10429,24 +10429,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10460,20 +10456,24 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -11209,17 +11209,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11236,23 +11236,23 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,27 +11561,31 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -11592,31 +11596,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,27 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,27 +13741,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13772,31 +13776,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13811,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,27 +13869,23 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -13900,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13954,20 +13954,24 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13981,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14012,23 +14012,27 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -14039,24 +14043,20 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
         <v>3</v>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,31 +14224,31 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -14259,23 +14259,23 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.127</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,23 +14290,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14321,27 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14356,19 +14360,19 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14376,11 +14380,11 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -14391,27 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14426,31 +14430,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -14461,27 +14461,23 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14496,31 +14492,31 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
+      <c r="F479" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -15027,23 +15027,27 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -15058,23 +15062,27 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G497" t="n">
@@ -15089,31 +15097,31 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -15124,31 +15132,27 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -15159,27 +15163,23 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.5%</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -16154,21 +16154,25 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16181,23 +16185,31 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -16208,21 +16220,29 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G539" t="n">
         <v>3</v>
       </c>
@@ -16235,23 +16255,31 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -16262,31 +16290,23 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
       <c r="G541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -16297,29 +16317,21 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
       <c r="G542" t="n">
         <v>3</v>
       </c>
@@ -16332,31 +16344,23 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
       <c r="G543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -16367,25 +16371,21 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>216.25K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F544" t="inlineStr"/>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16398,17 +16398,17 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E545" t="inlineStr"/>
@@ -16564,20 +16564,24 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>0.18M</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="n">
         <v>3</v>
@@ -16591,17 +16595,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E552" t="inlineStr"/>
@@ -16618,27 +16622,23 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>6.87%</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="554">
@@ -16649,17 +16649,17 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
@@ -16676,27 +16676,23 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr"/>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="556">
@@ -16707,17 +16703,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16734,23 +16730,27 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr"/>
+          <t>4.07M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -16761,23 +16761,27 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -16788,17 +16792,17 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E559" t="inlineStr"/>
@@ -16815,17 +16819,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E560" t="inlineStr"/>
@@ -16842,24 +16846,20 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>-1.2M</t>
-        </is>
-      </c>
+          <t>0.872M</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="n">
         <v>3</v>
@@ -16984,27 +16984,23 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -17019,27 +17015,27 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G568" t="n">
@@ -17054,20 +17050,24 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr"/>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F569" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17788,19 +17788,23 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17815,23 +17819,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -17869,27 +17877,23 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -17900,23 +17904,19 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -18020,19 +18020,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -18047,23 +18051,27 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="E604" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -18074,27 +18082,23 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -18132,23 +18136,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18753,19 +18753,23 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18838,23 +18842,19 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
       <c r="F637" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -18892,19 +18892,19 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -19076,13 +19076,13 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
@@ -19122,19 +19122,19 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="650">
@@ -19145,13 +19145,13 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
@@ -19168,13 +19168,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19191,19 +19191,19 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19214,13 +19214,13 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
@@ -19237,13 +19237,13 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
@@ -19260,19 +19260,19 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
@@ -19873,19 +19873,19 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="E678" t="inlineStr"/>
       <c r="F678" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G678" t="n">
@@ -19931,23 +19931,23 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G680" t="n">
@@ -20020,27 +20020,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -20051,27 +20051,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20082,13 +20078,13 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -20102,7 +20098,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20113,18 +20109,18 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -20133,7 +20129,7 @@
         </is>
       </c>
       <c r="G686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -20144,23 +20140,23 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -20175,23 +20171,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689">
@@ -20202,23 +20202,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E689" t="inlineStr"/>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G689" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="690">
@@ -20229,27 +20233,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G690" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
@@ -20260,23 +20264,19 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20426,25 +20426,13 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E697" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
       <c r="G697" t="n">
         <v>2</v>
       </c>
@@ -20457,13 +20445,25 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -21360,27 +21360,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -21422,27 +21422,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F737" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
@@ -21453,27 +21453,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="739">
@@ -21515,23 +21515,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21546,23 +21546,23 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -21577,23 +21577,19 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -21608,19 +21604,23 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G743" t="n">
@@ -21932,23 +21932,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G755" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="756">
@@ -22067,23 +22067,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="778">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22949,19 +22949,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -22976,19 +22976,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23003,23 +23003,23 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G800" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="801">
@@ -23030,23 +23030,23 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="802">
@@ -23084,19 +23084,19 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G803" t="n">
@@ -23111,23 +23111,23 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
@@ -23138,23 +23138,23 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="806">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -23344,7 +23344,7 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="816">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -23401,7 +23401,7 @@
       <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="819">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,17 +833,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,27 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,23 +922,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -945,27 +953,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,24 +980,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>3</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,31 +1980,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2019,31 +2011,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2054,27 +2046,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2089,31 +2081,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2124,23 +2116,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,27 +2507,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2685,20 +2685,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>3</v>
@@ -2712,27 +2716,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2743,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2774,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2828,27 +2824,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2859,23 +2855,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3406,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -4165,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4196,27 +4204,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4231,27 +4239,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4266,31 +4274,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4301,27 +4305,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,31 +4336,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4618,23 +4618,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5090,23 +5090,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5117,27 +5121,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5148,27 +5152,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,23 +5336,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5367,31 +5367,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -5402,31 +5402,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5437,23 +5437,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5464,27 +5472,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5499,23 +5507,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5530,17 +5542,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5557,25 +5569,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5588,27 +5596,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5623,21 +5631,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5650,17 +5662,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5677,29 +5689,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
         <v>3</v>
       </c>
@@ -5712,31 +5716,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5747,31 +5743,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5782,7 +5778,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5792,21 +5788,21 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5817,31 +5813,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5852,23 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,31 +6317,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -6352,27 +6348,23 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6387,27 +6379,31 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -6418,23 +6414,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -6993,27 +6993,31 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -7024,31 +7028,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -7059,27 +7063,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7349,17 +7357,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7376,20 +7384,24 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7403,17 +7415,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7430,27 +7442,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7461,17 +7469,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7488,27 +7496,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7519,24 +7523,20 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,27 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7736,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7806,27 +7810,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7841,31 +7845,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7880,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,27 +8306,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8341,31 +8337,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -8376,23 +8372,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,23 +9259,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -9282,24 +9290,20 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9313,17 +9317,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9340,20 +9344,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9367,17 +9375,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9394,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9425,27 +9429,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,27 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9607,31 +9603,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -9642,31 +9634,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9708,27 +9696,31 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9739,23 +9731,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9770,31 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9805,7 +9801,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9815,17 +9811,21 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -10429,24 +10429,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10460,20 +10456,24 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,23 +11155,23 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -11182,17 +11182,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -11209,17 +11209,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11236,23 +11236,23 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,31 +11561,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -11596,23 +11592,23 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -11627,27 +11623,31 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -13671,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13706,27 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,27 +13741,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13772,31 +13776,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13811,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -13842,24 +13842,20 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
         <v>3</v>
@@ -13873,27 +13869,23 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -13904,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13931,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13958,17 +13954,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -13985,27 +13981,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,23 +14008,27 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -14043,20 +14039,24 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
         <v>3</v>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,27 +14224,23 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>1880K</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14259,31 +14255,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -14294,31 +14290,31 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -14329,7 +14325,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -14342,14 +14338,18 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -14360,23 +14360,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,27 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14426,23 +14430,23 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>147.127</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14457,31 +14461,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -14492,31 +14496,31 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -14527,27 +14531,23 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,27 +14728,27 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="G487" t="n">
@@ -14763,23 +14763,23 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -14809,16 +14809,16 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -14829,27 +14829,31 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -14891,31 +14895,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -14926,31 +14930,27 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -14961,27 +14961,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -14992,31 +14996,27 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15768,17 +15768,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
@@ -15795,23 +15795,23 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -16154,23 +16154,31 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -16181,31 +16189,23 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -16216,17 +16216,17 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
@@ -16243,21 +16243,25 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G540" t="n">
         <v>3</v>
       </c>
@@ -16270,17 +16274,17 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="E541" t="inlineStr"/>
@@ -16297,31 +16301,23 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
       <c r="G542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -16332,29 +16328,21 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
       <c r="G543" t="n">
         <v>3</v>
       </c>
@@ -16367,21 +16355,29 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G544" t="n">
         <v>3</v>
       </c>
@@ -16394,27 +16390,31 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>216.25K</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -16564,27 +16564,23 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.082M</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="552">
@@ -16595,20 +16591,24 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>0.872M</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="n">
         <v>3</v>
@@ -16622,17 +16622,17 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E553" t="inlineStr"/>
@@ -16649,27 +16649,23 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr"/>
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -16680,17 +16676,17 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.87%</t>
         </is>
       </c>
       <c r="E555" t="inlineStr"/>
@@ -16707,17 +16703,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16734,23 +16730,27 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -16761,17 +16761,17 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="E558" t="inlineStr"/>
@@ -16788,27 +16788,27 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>-1.2M</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="560">
@@ -16819,17 +16819,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E560" t="inlineStr"/>
@@ -17085,27 +17085,31 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -17116,27 +17120,27 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G571" t="n">
@@ -17151,31 +17155,31 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G572" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -17186,31 +17190,31 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>4.08M</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>4.29M</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G573" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -17221,31 +17225,31 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -17256,31 +17260,27 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -17291,31 +17291,31 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>4.08M</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.29M</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G576" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E579" t="inlineStr"/>
@@ -17391,17 +17391,17 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -17788,19 +17788,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17842,19 +17842,19 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17989,23 +17989,27 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -18016,27 +18020,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -18374,15 +18374,19 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>$21.53T</t>
+        </is>
+      </c>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="inlineStr"/>
       <c r="G617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -18416,19 +18420,15 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -18604,19 +18604,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18627,19 +18627,19 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629">
@@ -18992,13 +18992,13 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr"/>
@@ -19115,13 +19115,13 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E648" t="inlineStr"/>
@@ -19138,19 +19138,19 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -19161,19 +19161,19 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
       <c r="F650" t="inlineStr"/>
       <c r="G650" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="651">
@@ -19207,13 +19207,13 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
@@ -19230,19 +19230,19 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654">
@@ -19253,13 +19253,13 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
@@ -19276,19 +19276,19 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
@@ -19510,21 +19510,17 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F665" t="inlineStr"/>
       <c r="G665" t="n">
         <v>3</v>
       </c>
@@ -19568,17 +19564,21 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G667" t="n">
         <v>3</v>
       </c>
@@ -19653,27 +19653,27 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G670" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -19951,23 +19951,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E680" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -19978,27 +19982,23 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -20009,27 +20009,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -20067,27 +20067,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685">
@@ -20098,13 +20098,13 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -20114,11 +20114,11 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20183,23 +20183,23 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G688" t="n">
@@ -20473,13 +20473,21 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -20492,21 +20500,13 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
+      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F699" t="inlineStr"/>
       <c r="G699" t="n">
         <v>2</v>
       </c>
@@ -20638,13 +20638,13 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E705" t="inlineStr"/>
@@ -20692,13 +20692,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20849,13 +20849,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -20918,13 +20918,13 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -22029,23 +22029,23 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G758" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="759">
@@ -22056,19 +22056,19 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G759" t="n">
@@ -22083,19 +22083,19 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G760" t="n">
@@ -22110,23 +22110,23 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G761" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -22603,7 +22603,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22857,19 +22857,19 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E794" t="inlineStr"/>
       <c r="F794" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G794" t="n">
@@ -22992,19 +22992,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23046,19 +23046,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23073,19 +23073,19 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G802" t="n">
@@ -23181,7 +23181,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -23189,7 +23189,7 @@
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr"/>
       <c r="G806" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -23322,7 +23322,7 @@
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="814">
@@ -23504,7 +23504,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -23903,19 +23903,23 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G840" t="n">
@@ -23930,27 +23934,23 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
       <c r="D841" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E841" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+          <t>$266.5B</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr"/>
       <c r="F841" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G841" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="842">
@@ -23961,21 +23961,13 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr"/>
       <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>$273.0B</t>
-        </is>
-      </c>
+      <c r="F842" t="inlineStr"/>
       <c r="G842" t="n">
         <v>2</v>
       </c>
@@ -23988,13 +23980,21 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
-      <c r="D843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E843" t="inlineStr"/>
-      <c r="F843" t="inlineStr"/>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G843" t="n">
         <v>2</v>
       </c>
@@ -24045,23 +24045,23 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G846" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="847">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-07.xlsx
@@ -806,23 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -833,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -887,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -914,24 +922,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>3</v>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1030,27 +1030,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,31 +1984,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2019,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2054,23 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.283M</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,31 +2507,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2685,27 +2685,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2716,20 +2712,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>3</v>
@@ -2743,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2774,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2828,23 +2824,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2882,27 +2882,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3336,31 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3406,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4204,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,27 +4235,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -4266,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4301,31 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5059,27 +5059,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5090,27 +5090,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5121,27 +5121,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5152,17 +5148,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5179,23 +5175,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,29 +5336,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5371,23 +5363,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5402,31 +5394,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5437,31 +5429,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5472,23 +5464,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5499,23 +5499,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5526,17 +5534,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5553,25 +5561,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5584,31 +5588,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5619,21 +5615,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -5708,31 +5708,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5753,21 +5753,21 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5778,31 +5778,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5813,23 +5809,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5844,27 +5844,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -5879,31 +5879,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -6282,27 +6282,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -6313,27 +6317,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,31 +6352,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6383,23 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6414,27 +6418,23 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6715,23 +6715,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6823,23 +6823,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7028,27 +7024,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -7059,31 +7059,31 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1853K</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -7241,23 +7241,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -7268,17 +7272,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7295,23 +7299,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -7322,17 +7330,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7349,24 +7357,20 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7380,17 +7384,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7407,27 +7411,23 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7465,27 +7465,23 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -7496,17 +7492,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7523,20 +7519,24 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7740,27 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr"/>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7841,31 +7845,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8306,27 +8306,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -8341,31 +8337,31 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -8376,23 +8372,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -8407,31 +8407,31 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>0.140%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8853,17 +8853,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.140%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9201,23 +9201,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -9228,17 +9232,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9255,23 +9259,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -9282,24 +9290,20 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
@@ -9313,17 +9317,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9340,20 +9344,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
         <v>3</v>
@@ -9367,27 +9375,23 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -9398,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,31 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9607,27 +9599,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1900K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9642,31 +9634,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9708,23 +9696,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9739,31 +9731,31 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -9774,7 +9766,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9784,17 +9776,21 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -9805,27 +9801,31 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -10429,24 +10429,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>582</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
         <v>3</v>
@@ -10460,20 +10456,24 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
         <v>3</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,27 +11561,31 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -11592,31 +11596,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
           <t>51.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.4</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -13636,27 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -13667,27 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -13702,31 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,27 +13741,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13772,31 +13776,27 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13807,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,27 +13869,23 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -13900,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13927,20 +13927,24 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
         <v>3</v>
@@ -13954,24 +13958,20 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13985,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,23 +14012,27 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -14043,17 +14043,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -14237,14 +14237,18 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -14255,23 +14259,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14286,31 +14294,31 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -14321,31 +14329,31 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -14356,27 +14364,23 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>1880K</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,23 +14395,23 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>147.127</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14422,31 +14426,31 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -14457,31 +14461,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -14492,27 +14496,23 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -14527,27 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1880K</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,27 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -14759,27 +14763,27 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,23 +14798,23 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G489" t="n">
@@ -14825,12 +14829,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -14840,16 +14844,16 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -14891,31 +14895,27 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -14926,27 +14926,31 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -14957,31 +14961,27 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -14992,31 +14992,31 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15768,17 +15768,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
@@ -15795,23 +15795,23 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -16154,21 +16154,25 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>215.25K</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>216.25K</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G537" t="n">
         <v>3</v>
       </c>
@@ -16181,29 +16185,21 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>1845K</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
         <v>3</v>
       </c>
@@ -16216,17 +16212,17 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>40.50</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
@@ -16243,31 +16239,23 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
       <c r="G540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -16278,17 +16266,17 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>40.50</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="E541" t="inlineStr"/>
@@ -16305,27 +16293,31 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>216.25K</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -16336,31 +16328,23 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>214K</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
       <c r="G543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -16371,23 +16355,31 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+          <t>214K</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -16398,21 +16390,29 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1869K</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
+          <t>1845K</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G545" t="n">
         <v>3</v>
       </c>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>6.87%</t>
         </is>
       </c>
       <c r="E551" t="inlineStr"/>
@@ -16591,27 +16591,23 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>4.07M</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.082M</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="553">
@@ -16622,20 +16618,24 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>0.872M</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr"/>
+          <t>0.135M</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-1.2M</t>
+        </is>
+      </c>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
         <v>3</v>
@@ -16649,27 +16649,23 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.159M</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr"/>
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -16680,17 +16676,17 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="E555" t="inlineStr"/>
@@ -16707,17 +16703,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -16734,23 +16730,27 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>0.159M</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr"/>
+          <t>-3.035M</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -16761,27 +16761,27 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>-1.2M</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -16792,17 +16792,17 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="E559" t="inlineStr"/>
@@ -16819,17 +16819,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E560" t="inlineStr"/>
@@ -17085,31 +17085,31 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>4.08M</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>4.29M</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G570" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -17120,27 +17120,31 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -17151,31 +17155,31 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G572" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -17186,31 +17190,27 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E573" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr"/>
       <c r="F573" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -17221,31 +17221,31 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -17256,31 +17256,31 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>4.08M</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.29M</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G575" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576">
@@ -17291,27 +17291,27 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G576" t="n">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E579" t="inlineStr"/>
@@ -17391,17 +17391,17 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -17788,19 +17788,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17842,19 +17842,19 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17989,23 +17989,27 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -18016,27 +18020,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18374,15 +18374,19 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>$21.53T</t>
+        </is>
+      </c>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="inlineStr"/>
       <c r="G617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -18416,19 +18420,15 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -18604,19 +18604,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18627,19 +18627,19 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629">
@@ -18992,19 +18992,19 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr"/>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -19115,19 +19115,19 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.151M</t>
         </is>
       </c>
       <c r="E648" t="inlineStr"/>
       <c r="F648" t="inlineStr"/>
       <c r="G648" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -19138,13 +19138,13 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.156M</t>
         </is>
       </c>
       <c r="E649" t="inlineStr"/>
@@ -19161,13 +19161,13 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E650" t="inlineStr"/>
@@ -19207,19 +19207,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19230,13 +19234,13 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.156M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
@@ -19253,19 +19257,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.151M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655">
@@ -19276,13 +19280,13 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
@@ -19438,7 +19442,11 @@
           <t>-0.7%</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr"/>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F662" t="inlineStr">
         <is>
           <t>0.1%</t>
@@ -19510,21 +19518,17 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F665" t="inlineStr"/>
       <c r="G665" t="n">
         <v>3</v>
       </c>
@@ -19568,17 +19572,21 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G667" t="n">
         <v>3</v>
       </c>
@@ -19653,27 +19661,27 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G670" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -19951,27 +19959,23 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E680" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr"/>
       <c r="F680" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -19982,23 +19986,23 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20013,27 +20017,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -20071,27 +20075,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685">
@@ -20102,13 +20106,13 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -20118,11 +20122,11 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20187,23 +20191,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
@@ -20473,13 +20481,21 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G698" t="n">
         <v>2</v>
       </c>
@@ -20492,21 +20508,13 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
+      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F699" t="inlineStr"/>
       <c r="G699" t="n">
         <v>2</v>
       </c>
@@ -20638,13 +20646,13 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E705" t="inlineStr"/>
@@ -20692,13 +20700,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20849,13 +20857,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -20918,13 +20926,13 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -22029,19 +22037,19 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G758" t="n">
@@ -22056,23 +22064,23 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G759" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -22083,23 +22091,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -22110,19 +22118,19 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G761" t="n">
@@ -22565,7 +22573,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -22603,7 +22611,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22857,19 +22865,19 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E794" t="inlineStr"/>
       <c r="F794" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G794" t="n">
@@ -22992,19 +23000,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23046,19 +23054,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23073,19 +23081,19 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G802" t="n">
@@ -23181,7 +23189,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -23504,7 +23512,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -23903,19 +23911,19 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E840" t="inlineStr"/>
       <c r="F840" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G840" t="n">
@@ -23930,23 +23938,23 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
       <c r="D841" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E841" t="inlineStr"/>
       <c r="F841" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G841" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842">
@@ -23976,19 +23984,23 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24041,27 +24053,23 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+          <t>$266.5B</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G846" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="847">
